--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -290,6 +290,18 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
@@ -622,7 +634,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -694,9 +706,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -2992,13 +3001,13 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="D6" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
         <x:v>90</x:v>
@@ -3010,19 +3019,19 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
-        <x:v>46084</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46083.1543634259</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>18</x:v>
@@ -3030,67 +3039,101 @@
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="20" t="s">
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="20" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C9" s="21" t="s"/>
-      <x:c r="D9" s="21" t="s"/>
-      <x:c r="E9" s="22" t="s"/>
-      <x:c r="F9" s="22" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="23" t="s">
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="22" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="23" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C10" s="24" t="s"/>
-      <x:c r="D10" s="24" t="s"/>
-      <x:c r="E10" s="24" t="s"/>
-      <x:c r="F10" s="25" t="s">
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="s">
         <x:v>87</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="26" t="s">
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="26" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="26" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s"/>
-      <x:c r="D11" s="27" t="s"/>
-      <x:c r="E11" s="27" t="s"/>
-      <x:c r="F11" s="28" t="n">
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="29" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="29" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s"/>
-      <x:c r="D12" s="30" t="s"/>
-      <x:c r="E12" s="30" t="s"/>
-      <x:c r="F12" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4071,13 +4114,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B10:F10"/>
     <x:mergeCell ref="B11:E11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -323,7 +287,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -350,12 +314,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -363,6 +321,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -377,13 +356,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -428,12 +400,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -445,14 +417,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -634,7 +606,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -645,190 +617,211 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1092,772 +1085,748 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="17">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="D8" s="19" t="s"/>
+      <x:c r="E8" s="19" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="F8" s="19" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="G8" s="19" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="H8" s="20">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="19" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="F9" s="19" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="G9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="L9" s="20">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C10" s="11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D10" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E10" s="11" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H10" s="13">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="C11" s="11" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="D11" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="E11" s="11" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="H11" s="13">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="15">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="D12" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F12" s="11" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G12" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H12" s="13">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I12" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="C13" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s"/>
+      <x:c r="E13" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I13" s="13">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I14" s="13">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="L14" s="15">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="C15" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="D15" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="F15" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="G15" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="H15" s="13">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="C16" s="11" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="D16" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="F16" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="G16" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="H16" s="13">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="D17" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="F17" s="11" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="G17" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="H17" s="13">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="D18" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="F18" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
+      <x:c r="G18" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="H18" s="13">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="C19" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="D19" s="12" t="s"/>
+      <x:c r="E19" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="F19" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="G19" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="H19" s="13">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="D20" s="12" t="s"/>
+      <x:c r="E20" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="F20" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="G20" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s"/>
-      <x:c r="E19" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="H20" s="13">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I20" s="13">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s"/>
-      <x:c r="E20" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
+      <x:c r="L20" s="15">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M20" s="11" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="20" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C23" s="21" t="s"/>
-      <x:c r="D23" s="21" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="22" t="s"/>
+      <x:c r="B23" s="23" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C23" s="24" t="s"/>
+      <x:c r="D23" s="24" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="25" t="s"/>
     </x:row>
     <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C24" s="24" t="s"/>
-      <x:c r="D24" s="24" t="s"/>
-      <x:c r="E24" s="24" t="s"/>
-      <x:c r="F24" s="25" t="s">
-        <x:v>87</x:v>
+      <x:c r="B24" s="26" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="B25" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="B26" s="29" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="B27" s="29" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="B28" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s"/>
+      <x:c r="D28" s="30" t="s"/>
+      <x:c r="E28" s="30" t="s"/>
+      <x:c r="F28" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="B29" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="B30" s="29" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="B31" s="29" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B33" s="32" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="29" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C33" s="30" t="s"/>
-      <x:c r="D33" s="30" t="s"/>
-      <x:c r="E33" s="30" t="s"/>
-      <x:c r="F33" s="31" t="n">
+      <x:c r="C33" s="33" t="s"/>
+      <x:c r="D33" s="33" t="s"/>
+      <x:c r="E33" s="33" t="s"/>
+      <x:c r="F33" s="34" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -2911,226 +2880,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I7" s="35">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="23" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="s"/>
+      <x:c r="D10" s="24" t="s"/>
+      <x:c r="E10" s="25" t="s"/>
+      <x:c r="F10" s="25" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="26" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s"/>
+      <x:c r="D11" s="27" t="s"/>
+      <x:c r="E11" s="27" t="s"/>
+      <x:c r="F11" s="28" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s"/>
+      <x:c r="D12" s="30" t="s"/>
+      <x:c r="E12" s="30" t="s"/>
+      <x:c r="F12" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="29" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s"/>
+      <x:c r="D13" s="30" t="s"/>
+      <x:c r="E13" s="30" t="s"/>
+      <x:c r="F13" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="B14" s="32" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C14" s="33" t="s"/>
+      <x:c r="D14" s="33" t="s"/>
+      <x:c r="E14" s="33" t="s"/>
+      <x:c r="F14" s="34" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,9 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DONNA GONZALES</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -690,7 +693,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -726,6 +729,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -745,34 +792,14 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -822,6 +849,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1070,7 +1101,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1087,7 +1120,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1148,22 +1181,22 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46066.2950925926</x:v>
@@ -1181,28 +1214,28 @@
         <x:v>46066.3194212963</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s"/>
       <x:c r="E7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>46072.1720833333</x:v>
@@ -1220,27 +1253,27 @@
         <x:v>46073.1890277778</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="19" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s"/>
       <x:c r="E8" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F8" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="20">
         <x:v>46063.2819560185</x:v>
@@ -1258,25 +1291,25 @@
         <x:v>46063.2957638889</x:v>
       </x:c>
       <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="19" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s"/>
       <x:c r="E9" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H9" s="20">
         <x:v>46058.4859837963</x:v>
@@ -1294,544 +1327,570 @@
         <x:v>46062.1881944444</x:v>
       </x:c>
       <x:c r="M9" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="D10" s="23" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="E10" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="G10" s="22" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H10" s="24">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>25</x:v>
+      <x:c r="M10" s="22" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="D11" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="E11" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="G11" s="22" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="24">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I11" s="22">
+      <x:c r="I11" s="27">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M11" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="B12" s="22" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="D12" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="F12" s="22" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="G12" s="22" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H12" s="24">
         <x:v>46072.3529513889</x:v>
       </x:c>
-      <x:c r="I12" s="22">
+      <x:c r="I12" s="27">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="23" t="n">
         <x:v>1507785</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="26">
         <x:v>46073.2314351852</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M12" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s"/>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="C13" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="F13" s="22" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="G13" s="22" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="24">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="I13" s="13">
+      <x:c r="I13" s="24">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="23" t="n">
         <x:v>1507791</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="25" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="26">
         <x:v>46073.3142476852</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M13" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="C14" s="22" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="D14" s="23" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="F14" s="22" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="G14" s="22" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="24">
         <x:v>46058.1529282407</x:v>
       </x:c>
-      <x:c r="I14" s="13">
+      <x:c r="I14" s="24">
         <x:v>46058.1529398148</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="23" t="n">
         <x:v>1507657</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="26">
         <x:v>46058.2410648148</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M14" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="C15" s="22" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="D15" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="F15" s="22" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="G15" s="22" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="24">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I15" s="22">
+      <x:c r="I15" s="27">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="23" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="25" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="26">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M15" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="C16" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="D16" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="F16" s="22" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="G16" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H16" s="24">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I16" s="22">
+      <x:c r="I16" s="27">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="23" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="26">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M16" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="B17" s="22" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="D17" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="F17" s="22" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="G17" s="22" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H17" s="24">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I17" s="22">
+      <x:c r="I17" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="23" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="26">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M17" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="B18" s="22" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="D18" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="F18" s="22" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="G18" s="22" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="24">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I18" s="22">
+      <x:c r="I18" s="27">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="23" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="26">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M18" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s"/>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="C19" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="22" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="F19" s="22" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="G19" s="22" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H19" s="24">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I19" s="13">
+      <x:c r="I19" s="24">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="23" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="K19" s="25" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L19" s="15">
+      <x:c r="L19" s="26">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
-        <x:v>6</x:v>
+      <x:c r="M19" s="22" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s"/>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="B20" s="22" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="F20" s="22" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="G20" s="22" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H20" s="24">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I20" s="13">
+      <x:c r="I20" s="24">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="23" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="K20" s="25" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L20" s="15">
+      <x:c r="L20" s="26">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C23" s="24" t="s"/>
-      <x:c r="D23" s="24" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="25" t="s"/>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="M20" s="22" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B21" s="28" t="s"/>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="28" t="s"/>
+      <x:c r="G21" s="28" t="s"/>
+      <x:c r="H21" s="28" t="s"/>
+      <x:c r="I21" s="28" t="s"/>
+      <x:c r="J21" s="28" t="s"/>
+      <x:c r="K21" s="28" t="s"/>
+      <x:c r="L21" s="28" t="s"/>
+      <x:c r="M21" s="28" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B22" s="28" t="s"/>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="28" t="s"/>
+      <x:c r="G22" s="28" t="s"/>
+      <x:c r="H22" s="28" t="s"/>
+      <x:c r="I22" s="28" t="s"/>
+      <x:c r="J22" s="28" t="s"/>
+      <x:c r="K22" s="28" t="s"/>
+      <x:c r="L22" s="28" t="s"/>
+      <x:c r="M22" s="28" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="29" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="29" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="30" t="s"/>
       <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="E25" s="31" t="s"/>
+      <x:c r="F25" s="31" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="32" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C26" s="33" t="s"/>
+      <x:c r="D26" s="33" t="s"/>
+      <x:c r="E26" s="33" t="s"/>
+      <x:c r="F26" s="34" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="35" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C27" s="36" t="s"/>
+      <x:c r="D27" s="36" t="s"/>
+      <x:c r="E27" s="36" t="s"/>
+      <x:c r="F27" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="29" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="35" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C28" s="36" t="s"/>
+      <x:c r="D28" s="36" t="s"/>
+      <x:c r="E28" s="36" t="s"/>
+      <x:c r="F28" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="29" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="35" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C29" s="36" t="s"/>
+      <x:c r="D29" s="36" t="s"/>
+      <x:c r="E29" s="36" t="s"/>
+      <x:c r="F29" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="29" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C28" s="30" t="s"/>
-      <x:c r="D28" s="30" t="s"/>
-      <x:c r="E28" s="30" t="s"/>
-      <x:c r="F28" s="31" t="n">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="35" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C30" s="36" t="s"/>
+      <x:c r="D30" s="36" t="s"/>
+      <x:c r="E30" s="36" t="s"/>
+      <x:c r="F30" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C29" s="30" t="s"/>
-      <x:c r="D29" s="30" t="s"/>
-      <x:c r="E29" s="30" t="s"/>
-      <x:c r="F29" s="31" t="n">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="35" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C31" s="36" t="s"/>
+      <x:c r="D31" s="36" t="s"/>
+      <x:c r="E31" s="36" t="s"/>
+      <x:c r="F31" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="29" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C30" s="30" t="s"/>
-      <x:c r="D30" s="30" t="s"/>
-      <x:c r="E30" s="30" t="s"/>
-      <x:c r="F30" s="31" t="n">
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="35" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C32" s="36" t="s"/>
+      <x:c r="D32" s="36" t="s"/>
+      <x:c r="E32" s="36" t="s"/>
+      <x:c r="F32" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="29" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C31" s="30" t="s"/>
-      <x:c r="D31" s="30" t="s"/>
-      <x:c r="E31" s="30" t="s"/>
-      <x:c r="F31" s="31" t="n">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="35" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C33" s="36" t="s"/>
+      <x:c r="D33" s="36" t="s"/>
+      <x:c r="E33" s="36" t="s"/>
+      <x:c r="F33" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="29" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C32" s="30" t="s"/>
-      <x:c r="D32" s="30" t="s"/>
-      <x:c r="E32" s="30" t="s"/>
-      <x:c r="F32" s="31" t="n">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="35" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C34" s="36" t="s"/>
+      <x:c r="D34" s="36" t="s"/>
+      <x:c r="E34" s="36" t="s"/>
+      <x:c r="F34" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="32" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C33" s="33" t="s"/>
-      <x:c r="D33" s="33" t="s"/>
-      <x:c r="E33" s="33" t="s"/>
-      <x:c r="F33" s="34" t="n">
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="38" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C35" s="39" t="s"/>
+      <x:c r="D35" s="39" t="s"/>
+      <x:c r="E35" s="39" t="s"/>
+      <x:c r="F35" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2791,12 +2850,11 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="13">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B23:F23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
+  <x:mergeCells count="14">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
@@ -2805,6 +2863,8 @@
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2865,7 +2925,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2943,24 +3005,24 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46085.1627430556</x:v>
@@ -2978,35 +3040,35 @@
         <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="16" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I7" s="35">
+      <x:c r="I7" s="41">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="J7" s="16" t="n">
@@ -3019,94 +3081,94 @@
         <x:v>46083.1543634259</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C10" s="24" t="s"/>
-      <x:c r="D10" s="24" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="25" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="26" t="s">
+      <x:c r="B8" s="42" t="s"/>
+      <x:c r="C8" s="42" t="s"/>
+      <x:c r="D8" s="42" t="s"/>
+      <x:c r="E8" s="42" t="s"/>
+      <x:c r="F8" s="42" t="s"/>
+      <x:c r="G8" s="42" t="s"/>
+      <x:c r="H8" s="42" t="s"/>
+      <x:c r="I8" s="42" t="s"/>
+      <x:c r="J8" s="42" t="s"/>
+      <x:c r="K8" s="42" t="s"/>
+      <x:c r="L8" s="42" t="s"/>
+      <x:c r="M8" s="42" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="42" t="s"/>
+      <x:c r="C9" s="42" t="s"/>
+      <x:c r="D9" s="42" t="s"/>
+      <x:c r="E9" s="42" t="s"/>
+      <x:c r="F9" s="42" t="s"/>
+      <x:c r="G9" s="42" t="s"/>
+      <x:c r="H9" s="42" t="s"/>
+      <x:c r="I9" s="42" t="s"/>
+      <x:c r="J9" s="42" t="s"/>
+      <x:c r="K9" s="42" t="s"/>
+      <x:c r="L9" s="42" t="s"/>
+      <x:c r="M9" s="42" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="29" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s"/>
-      <x:c r="D11" s="27" t="s"/>
-      <x:c r="E11" s="27" t="s"/>
-      <x:c r="F11" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="30" t="s"/>
       <x:c r="D12" s="30" t="s"/>
-      <x:c r="E12" s="30" t="s"/>
-      <x:c r="F12" s="31" t="n">
+      <x:c r="E12" s="31" t="s"/>
+      <x:c r="F12" s="31" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="32" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C13" s="33" t="s"/>
+      <x:c r="D13" s="33" t="s"/>
+      <x:c r="E13" s="33" t="s"/>
+      <x:c r="F13" s="34" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="35" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C14" s="36" t="s"/>
+      <x:c r="D14" s="36" t="s"/>
+      <x:c r="E14" s="36" t="s"/>
+      <x:c r="F14" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C13" s="30" t="s"/>
-      <x:c r="D13" s="30" t="s"/>
-      <x:c r="E13" s="30" t="s"/>
-      <x:c r="F13" s="31" t="n">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="35" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C15" s="36" t="s"/>
+      <x:c r="D15" s="36" t="s"/>
+      <x:c r="E15" s="36" t="s"/>
+      <x:c r="F15" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="32" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="s"/>
-      <x:c r="D14" s="33" t="s"/>
-      <x:c r="E14" s="33" t="s"/>
-      <x:c r="F14" s="34" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="38" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C16" s="39" t="s"/>
+      <x:c r="D16" s="39" t="s"/>
+      <x:c r="E16" s="39" t="s"/>
+      <x:c r="F16" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4085,14 +4147,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -1151,7 +1151,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1219,7 +1219,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -2975,7 +2975,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3045,7 +3045,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>52</x:v>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,12 +23,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>DONNA GONZALES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -290,7 +326,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -335,21 +371,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -359,6 +380,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -609,7 +637,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -620,80 +648,71 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -724,56 +743,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -788,71 +759,79 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1153,18 +1132,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1182,712 +1149,724 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s"/>
-      <x:c r="E8" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H9" s="20">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I11" s="16">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E10" s="22" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H10" s="24">
+      <x:c r="M11" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I12" s="16">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K10" s="25" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="26">
+      <x:c r="L12" s="18">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
+      <x:c r="M12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I11" s="27">
+      <x:c r="I13" s="19">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="26">
+      <x:c r="L13" s="18">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="s">
+      <x:c r="M13" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F12" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I12" s="27">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J12" s="23" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K12" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="26">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="22" t="s">
+      <x:c r="E16" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H13" s="24">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I13" s="24">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J13" s="23" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K13" s="25" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L13" s="26">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E14" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="22" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="24">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I14" s="24">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J14" s="23" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K14" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="26">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M14" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G15" s="22" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H15" s="24">
+      <x:c r="E17" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I15" s="27">
+      <x:c r="I17" s="19">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J15" s="23" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K15" s="25" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L15" s="26">
+      <x:c r="L17" s="18">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M15" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D16" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E16" s="22" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G16" s="22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H16" s="24">
+      <x:c r="M17" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I16" s="27">
+      <x:c r="I18" s="19">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J16" s="23" t="n">
+      <x:c r="J18" s="15" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K16" s="25" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="26">
+      <x:c r="L18" s="18">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M16" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D17" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E17" s="22" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G17" s="22" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H17" s="24">
+      <x:c r="M18" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I17" s="27">
+      <x:c r="I19" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J17" s="23" t="n">
+      <x:c r="J19" s="15" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K17" s="25" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L17" s="26">
+      <x:c r="L19" s="18">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M17" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E18" s="22" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G18" s="22" t="s">
+      <x:c r="M19" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H18" s="24">
+      <x:c r="C20" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I18" s="27">
+      <x:c r="I20" s="19">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J18" s="23" t="n">
+      <x:c r="J20" s="15" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K18" s="25" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="26">
+      <x:c r="L20" s="18">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M18" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="22" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F19" s="22" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G19" s="22" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H19" s="24">
+      <x:c r="M20" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s"/>
+      <x:c r="E21" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I19" s="24">
+      <x:c r="I21" s="16">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J19" s="23" t="n">
+      <x:c r="J21" s="15" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K19" s="25" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L19" s="26">
+      <x:c r="L21" s="18">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M19" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H20" s="24">
+      <x:c r="M21" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s"/>
+      <x:c r="E22" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I20" s="24">
+      <x:c r="I22" s="16">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J20" s="23" t="n">
+      <x:c r="J22" s="15" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K20" s="25" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L20" s="26">
+      <x:c r="L22" s="18">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M20" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B21" s="28" t="s"/>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="28" t="s"/>
-      <x:c r="G21" s="28" t="s"/>
-      <x:c r="H21" s="28" t="s"/>
-      <x:c r="I21" s="28" t="s"/>
-      <x:c r="J21" s="28" t="s"/>
-      <x:c r="K21" s="28" t="s"/>
-      <x:c r="L21" s="28" t="s"/>
-      <x:c r="M21" s="28" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B22" s="28" t="s"/>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="28" t="s"/>
-      <x:c r="G22" s="28" t="s"/>
-      <x:c r="H22" s="28" t="s"/>
-      <x:c r="I22" s="28" t="s"/>
-      <x:c r="J22" s="28" t="s"/>
-      <x:c r="K22" s="28" t="s"/>
-      <x:c r="L22" s="28" t="s"/>
-      <x:c r="M22" s="28" t="s"/>
+      <x:c r="M22" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="29" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="31" t="s"/>
-      <x:c r="F25" s="31" t="s"/>
+      <x:c r="B25" s="20" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C25" s="21" t="s"/>
+      <x:c r="D25" s="21" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="22" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="32" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="s"/>
-      <x:c r="D26" s="33" t="s"/>
-      <x:c r="E26" s="33" t="s"/>
-      <x:c r="F26" s="34" t="s">
-        <x:v>76</x:v>
+      <x:c r="B26" s="23" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C26" s="24" t="s"/>
+      <x:c r="D26" s="24" t="s"/>
+      <x:c r="E26" s="24" t="s"/>
+      <x:c r="F26" s="25" t="s">
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="35" t="s">
+      <x:c r="B27" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C27" s="36" t="s"/>
-      <x:c r="D27" s="36" t="s"/>
-      <x:c r="E27" s="36" t="s"/>
-      <x:c r="F27" s="37" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="35" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C28" s="36" t="s"/>
-      <x:c r="D28" s="36" t="s"/>
-      <x:c r="E28" s="36" t="s"/>
-      <x:c r="F28" s="37" t="n">
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="35" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C29" s="36" t="s"/>
-      <x:c r="D29" s="36" t="s"/>
-      <x:c r="E29" s="36" t="s"/>
-      <x:c r="F29" s="37" t="n">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="35" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C30" s="36" t="s"/>
-      <x:c r="D30" s="36" t="s"/>
-      <x:c r="E30" s="36" t="s"/>
-      <x:c r="F30" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="35" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C31" s="36" t="s"/>
-      <x:c r="D31" s="36" t="s"/>
-      <x:c r="E31" s="36" t="s"/>
-      <x:c r="F31" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="35" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C32" s="36" t="s"/>
-      <x:c r="D32" s="36" t="s"/>
-      <x:c r="E32" s="36" t="s"/>
-      <x:c r="F32" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="35" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C33" s="36" t="s"/>
-      <x:c r="D33" s="36" t="s"/>
-      <x:c r="E33" s="36" t="s"/>
-      <x:c r="F33" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="35" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C34" s="36" t="s"/>
-      <x:c r="D34" s="36" t="s"/>
-      <x:c r="E34" s="36" t="s"/>
-      <x:c r="F34" s="37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="38" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C35" s="39" t="s"/>
-      <x:c r="D35" s="39" t="s"/>
-      <x:c r="E35" s="39" t="s"/>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="B35" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -2977,18 +2956,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3006,166 +2973,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I7" s="41">
+      <x:c r="I9" s="32">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J7" s="16" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K7" s="18" t="n">
+      <x:c r="K9" s="13" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L7" s="17">
+      <x:c r="L9" s="12">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="42" t="s"/>
-      <x:c r="C8" s="42" t="s"/>
-      <x:c r="D8" s="42" t="s"/>
-      <x:c r="E8" s="42" t="s"/>
-      <x:c r="F8" s="42" t="s"/>
-      <x:c r="G8" s="42" t="s"/>
-      <x:c r="H8" s="42" t="s"/>
-      <x:c r="I8" s="42" t="s"/>
-      <x:c r="J8" s="42" t="s"/>
-      <x:c r="K8" s="42" t="s"/>
-      <x:c r="L8" s="42" t="s"/>
-      <x:c r="M8" s="42" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="42" t="s"/>
-      <x:c r="C9" s="42" t="s"/>
-      <x:c r="D9" s="42" t="s"/>
-      <x:c r="E9" s="42" t="s"/>
-      <x:c r="F9" s="42" t="s"/>
-      <x:c r="G9" s="42" t="s"/>
-      <x:c r="H9" s="42" t="s"/>
-      <x:c r="I9" s="42" t="s"/>
-      <x:c r="J9" s="42" t="s"/>
-      <x:c r="K9" s="42" t="s"/>
-      <x:c r="L9" s="42" t="s"/>
-      <x:c r="M9" s="42" t="s"/>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C12" s="30" t="s"/>
-      <x:c r="D12" s="30" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="31" t="s"/>
+      <x:c r="B12" s="20" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="32" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="s"/>
-      <x:c r="D13" s="33" t="s"/>
-      <x:c r="E13" s="33" t="s"/>
-      <x:c r="F13" s="34" t="s">
-        <x:v>76</x:v>
+      <x:c r="B13" s="23" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="35" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="36" t="s"/>
-      <x:c r="D14" s="36" t="s"/>
-      <x:c r="E14" s="36" t="s"/>
-      <x:c r="F14" s="37" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="35" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="36" t="s"/>
-      <x:c r="D15" s="36" t="s"/>
-      <x:c r="E15" s="36" t="s"/>
-      <x:c r="F15" s="37" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="38" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="s"/>
-      <x:c r="D16" s="39" t="s"/>
-      <x:c r="E16" s="39" t="s"/>
-      <x:c r="F16" s="40" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -293,6 +293,18 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBEN C. SESCON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blk. 17, Lot 14, Phase 2 Aquino Street, Citihomes, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIV-A-07321-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1203-366</x:t>
   </x:si>
   <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
@@ -637,7 +649,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -708,11 +720,8 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -829,10 +838,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -3019,14 +3024,12 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
+      <x:c r="D8" s="11" t="s"/>
       <x:c r="E8" s="11" t="s">
         <x:v>91</x:v>
       </x:c>
@@ -3037,19 +3040,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H8" s="12">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46098.0792592593</x:v>
       </x:c>
       <x:c r="I8" s="12">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46098.0878935185</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1529776</x:v>
       </x:c>
       <x:c r="K8" s="13" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L8" s="12">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46098.0997569444</x:v>
       </x:c>
       <x:c r="M8" s="11" t="s">
         <x:v>19</x:v>
@@ -3057,13 +3060,13 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
         <x:v>95</x:v>
@@ -3075,60 +3078,87 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H9" s="12">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I9" s="32">
-        <x:v>46084</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J9" s="11" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K9" s="13" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="12">
-        <x:v>46083.1543634259</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M9" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="26" t="s">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="27" t="s"/>
       <x:c r="D15" s="27" t="s"/>
@@ -3137,19 +3167,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4126,15 +4176,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -31,6 +31,9 @@
     <x:t>DONNA GONZALES</x:t>
   </x:si>
   <x:si>
+    <x:t>IV-A | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -293,6 +296,9 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>RUBEN C. SESCON</x:t>
@@ -338,7 +344,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -378,6 +384,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -649,14 +679,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -669,59 +708,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -752,91 +791,103 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1065,58 +1116,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1159,719 +1210,719 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46066.3145023148</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1507747</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46066.3194212963</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="12">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="L10" s="21">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="21">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="B12" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
+      <x:c r="C12" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D12" s="18" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="E12" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="F12" s="17" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="G12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="19">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="21">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>38</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="B13" s="17" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
+      <x:c r="C13" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="D13" s="18" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="E13" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="F13" s="17" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="G13" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I13" s="22">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="21">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="B14" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="D14" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="F14" s="17" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="G14" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>46072.3529513889</x:v>
       </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="I14" s="22">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>1507785</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="21">
         <x:v>46073.2314351852</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="B15" s="17" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="C15" s="17" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="F15" s="17" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="G15" s="17" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="I15" s="19">
         <x:v>46073.2761689815</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1507791</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="20" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="21">
         <x:v>46073.3142476852</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="B16" s="17" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="C16" s="17" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="D16" s="18" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="F16" s="17" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="G16" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
         <x:v>46058.1529282407</x:v>
       </x:c>
-      <x:c r="I16" s="16">
+      <x:c r="I16" s="19">
         <x:v>46058.1529398148</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>1507657</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K16" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L16" s="21">
         <x:v>46058.2410648148</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M16" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="B17" s="17" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="C17" s="17" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="D17" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="F17" s="17" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="G17" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="I17" s="22">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="18" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="K17" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L17" s="18">
+      <x:c r="L17" s="21">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M17" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="B18" s="17" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="C18" s="17" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="D18" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="F18" s="17" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="G18" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="I18" s="22">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J18" s="18" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="21">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M18" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="B19" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="D19" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="F19" s="17" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="G19" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="I19" s="22">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="18" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="K19" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L19" s="18">
+      <x:c r="L19" s="21">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M19" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
+      <x:c r="B20" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="D20" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="F20" s="17" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="H20" s="16">
+      <x:c r="G20" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="I20" s="22">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
+      <x:c r="J20" s="18" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="K20" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L20" s="18">
+      <x:c r="L20" s="21">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M20" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="B21" s="17" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s"/>
-      <x:c r="E21" s="14" t="s">
+      <x:c r="C21" s="17" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="D21" s="18" t="s"/>
+      <x:c r="E21" s="17" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="F21" s="17" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="H21" s="16">
+      <x:c r="G21" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I21" s="16">
+      <x:c r="I21" s="19">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
+      <x:c r="J21" s="18" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="K21" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L21" s="18">
+      <x:c r="L21" s="21">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M21" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s"/>
-      <x:c r="E22" s="14" t="s">
+      <x:c r="B22" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="D22" s="18" t="s"/>
+      <x:c r="E22" s="17" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="F22" s="17" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H22" s="16">
+      <x:c r="G22" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I22" s="16">
+      <x:c r="I22" s="19">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J22" s="15" t="n">
+      <x:c r="J22" s="18" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K22" s="17" t="n">
+      <x:c r="K22" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L22" s="18">
+      <x:c r="L22" s="21">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M22" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="20" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C25" s="21" t="s"/>
-      <x:c r="D25" s="21" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="22" t="s"/>
+      <x:c r="B25" s="23" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C25" s="24" t="s"/>
+      <x:c r="D25" s="24" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="25" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="s">
+      <x:c r="B26" s="26" t="s">
         <x:v>88</x:v>
       </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="B27" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="B28" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s"/>
+      <x:c r="D28" s="30" t="s"/>
+      <x:c r="E28" s="30" t="s"/>
+      <x:c r="F28" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="B29" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="B30" s="29" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="B31" s="29" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="B32" s="29" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="B33" s="29" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="B34" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="29" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C35" s="30" t="s"/>
-      <x:c r="D35" s="30" t="s"/>
-      <x:c r="E35" s="30" t="s"/>
-      <x:c r="F35" s="31" t="n">
+      <x:c r="B35" s="32" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C35" s="33" t="s"/>
+      <x:c r="D35" s="33" t="s"/>
+      <x:c r="E35" s="33" t="s"/>
+      <x:c r="F35" s="34" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -2837,7 +2888,7 @@
   <x:mergeCells count="14">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
@@ -2889,58 +2940,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2983,220 +3034,220 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46098.0792592593</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46098.0878935185</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1529776</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46098.0997569444</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="F9" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46085.1627430556</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="15">
         <x:v>46085.1627546296</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1507966</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46090.3453472222</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D10" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="F10" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="22">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="23" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="25" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>88</x:v>
       </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="29" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="B18" s="32" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C18" s="33" t="s"/>
+      <x:c r="D18" s="33" t="s"/>
+      <x:c r="E18" s="33" t="s"/>
+      <x:c r="F18" s="34" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4179,7 +4230,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,6 +68,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -341,10 +377,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -389,15 +427,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -413,15 +443,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -684,21 +707,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -708,59 +731,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -791,103 +814,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1116,78 +1127,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28">
-      <x:c r="A5" s="4" t="s"/>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1208,7 +1231,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1248,686 +1271,736 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46066.3145023148</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1507747</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46066.3194212963</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s"/>
+      <x:c r="E17" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s"/>
+      <x:c r="E23" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s"/>
+      <x:c r="E24" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="20" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C27" s="21" t="s"/>
+      <x:c r="D27" s="21" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="22" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="23" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C28" s="24" t="s"/>
+      <x:c r="D28" s="24" t="s"/>
+      <x:c r="E28" s="24" t="s"/>
+      <x:c r="F28" s="25" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="29" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I13" s="22">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I14" s="22">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s"/>
-      <x:c r="E15" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I17" s="22">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I18" s="22">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I19" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I20" s="22">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s"/>
-      <x:c r="E21" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s"/>
-      <x:c r="E22" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C25" s="24" t="s"/>
-      <x:c r="D25" s="24" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="25" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="29" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C28" s="30" t="s"/>
-      <x:c r="D28" s="30" t="s"/>
-      <x:c r="E28" s="30" t="s"/>
-      <x:c r="F28" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C29" s="30" t="s"/>
-      <x:c r="D29" s="30" t="s"/>
-      <x:c r="E29" s="30" t="s"/>
-      <x:c r="F29" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="29" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="30" t="s"/>
-      <x:c r="D30" s="30" t="s"/>
-      <x:c r="E30" s="30" t="s"/>
-      <x:c r="F30" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C31" s="30" t="s"/>
-      <x:c r="D31" s="30" t="s"/>
-      <x:c r="E31" s="30" t="s"/>
-      <x:c r="F31" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C32" s="30" t="s"/>
-      <x:c r="D32" s="30" t="s"/>
-      <x:c r="E32" s="30" t="s"/>
-      <x:c r="F32" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="29" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C33" s="30" t="s"/>
-      <x:c r="D33" s="30" t="s"/>
-      <x:c r="E33" s="30" t="s"/>
-      <x:c r="F33" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="29" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C34" s="30" t="s"/>
-      <x:c r="D34" s="30" t="s"/>
-      <x:c r="E34" s="30" t="s"/>
-      <x:c r="F34" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="32" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C35" s="33" t="s"/>
-      <x:c r="D35" s="33" t="s"/>
-      <x:c r="E35" s="33" t="s"/>
-      <x:c r="F35" s="34" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2885,13 +2958,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="14">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="15">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B25:F25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
@@ -2900,6 +2972,8 @@
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2940,78 +3014,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3032,7 +3118,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3072,187 +3158,237 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46098.0792592593</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46098.0878935185</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1529776</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46098.0997569444</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="20" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I10" s="22">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="25" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="32" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="s"/>
-      <x:c r="D18" s="33" t="s"/>
-      <x:c r="E18" s="33" t="s"/>
-      <x:c r="F18" s="34" t="n">
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4227,16 +4363,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,42 +68,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -382,7 +346,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -426,14 +390,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -445,6 +401,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -702,7 +673,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -710,16 +681,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -731,13 +702,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -749,41 +714,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -814,28 +788,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -850,55 +816,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1231,7 +1213,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1271,736 +1253,686 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="F10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="H10" s="19">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="F11" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="G11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="L11" s="21">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="C12" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="D12" s="18" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="E12" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="F12" s="17" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="G12" s="17" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="H12" s="19">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="D13" s="18" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="E13" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="F13" s="17" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="G13" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="B14" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="F14" s="17" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="G14" s="17" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="H14" s="19">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="C15" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46073.2761689815</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1507791</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46073.3142476852</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="L16" s="21">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s"/>
+      <x:c r="E21" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s"/>
+      <x:c r="E22" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="22" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="s"/>
+      <x:c r="D25" s="23" t="s"/>
+      <x:c r="E25" s="24" t="s"/>
+      <x:c r="F25" s="24" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="25" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="28" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C28" s="29" t="s"/>
+      <x:c r="D28" s="29" t="s"/>
+      <x:c r="E28" s="29" t="s"/>
+      <x:c r="F28" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="28" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="28" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="C31" s="29" t="s"/>
+      <x:c r="D31" s="29" t="s"/>
+      <x:c r="E31" s="29" t="s"/>
+      <x:c r="F31" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="28" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s"/>
-      <x:c r="E17" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="28" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="28" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="31" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s"/>
-      <x:c r="E23" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s"/>
-      <x:c r="E24" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="20" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C27" s="21" t="s"/>
-      <x:c r="D27" s="21" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="22" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="23" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C28" s="24" t="s"/>
-      <x:c r="D28" s="24" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="25" t="s">
-        <x:v>101</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
+      <x:c r="C35" s="32" t="s"/>
+      <x:c r="D35" s="32" t="s"/>
+      <x:c r="E35" s="32" t="s"/>
+      <x:c r="F35" s="33" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2963,7 +2895,9 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B27:F27"/>
+    <x:mergeCell ref="B25:F25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
@@ -2972,8 +2906,6 @@
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3085,7 +3017,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3118,7 +3050,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3158,237 +3090,187 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="B10" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I10" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L10" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
-        <x:v>101</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="22" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="24" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="25" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="28" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="31" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4368,12 +4250,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -299,6 +299,24 @@
   </x:si>
   <x:si>
     <x:t>IV-A | March 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHRISTOPHER I. PALLESCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03055C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1210-786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02054C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1209-851</x:t>
   </x:si>
   <x:si>
     <x:t>RUBEN C. SESCON</x:t>
@@ -3109,19 +3127,19 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46098.0792592593</x:v>
+        <x:v>46100.3734490741</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46098.0878935185</x:v>
+        <x:v>46100.388599537</x:v>
       </x:c>
       <x:c r="J8" s="14" t="n">
-        <x:v>1529776</x:v>
+        <x:v>1529812</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46098.0997569444</x:v>
+        <x:v>46100.3957175926</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
@@ -3129,37 +3147,35 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="H9" s="15">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46100.365787037</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46100.3731712963</x:v>
       </x:c>
       <x:c r="J9" s="14" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1529809</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="15">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46100.3868981482</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
@@ -3167,110 +3183,182 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="17" t="s">
-        <x:v>65</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="H10" s="19">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46098.0792592593</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46084</x:v>
+        <x:v>46098.0878935185</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1529776</x:v>
       </x:c>
       <x:c r="K10" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="21">
-        <x:v>46083.1543634259</x:v>
+        <x:v>46098.0997569444</x:v>
       </x:c>
       <x:c r="M10" s="17" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="24" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="24" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="s">
         <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s"/>
       <x:c r="D17" s="29" t="s"/>
       <x:c r="E17" s="29" t="s"/>
       <x:c r="F17" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="28" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="28" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="31" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4250,12 +4338,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -85,6 +85,9 @@
     <x:t>43A-2-2026-1076-698</x:t>
   </x:si>
   <x:si>
+    <x:t>1507747</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ricardo Natividad</x:t>
   </x:si>
   <x:si>
@@ -100,6 +103,9 @@
     <x:t>43A-2-2026-1103-424</x:t>
   </x:si>
   <x:si>
+    <x:t>1507783</x:t>
+  </x:si>
+  <x:si>
     <x:t>RASEL C. FERRER</x:t>
   </x:si>
   <x:si>
@@ -112,6 +118,9 @@
     <x:t>43A-2-2026-1072-268</x:t>
   </x:si>
   <x:si>
+    <x:t>1507682</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROFIEN F. NUÑEZ</x:t>
   </x:si>
   <x:si>
@@ -124,6 +133,9 @@
     <x:t>43A-2-2026-1061-611</x:t>
   </x:si>
   <x:si>
+    <x:t>1507672</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -142,6 +154,9 @@
     <x:t>43A-2-2026-1105-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1505803</x:t>
+  </x:si>
+  <x:si>
     <x:t>Deniel Puyo</x:t>
   </x:si>
   <x:si>
@@ -163,6 +178,9 @@
     <x:t>43A-2-2026-1107-513</x:t>
   </x:si>
   <x:si>
+    <x:t>1507784</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAR APPLIANCE CENTER, INC. - (BRANCH)</x:t>
   </x:si>
   <x:si>
@@ -175,6 +193,9 @@
     <x:t>43A-2-2026-1106-738</x:t>
   </x:si>
   <x:si>
+    <x:t>1507785</x:t>
+  </x:si>
+  <x:si>
     <x:t>Duplicate Copy</x:t>
   </x:si>
   <x:si>
@@ -190,6 +211,9 @@
     <x:t>43A-2-2026-1114-391</x:t>
   </x:si>
   <x:si>
+    <x:t>1507791</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -205,6 +229,9 @@
     <x:t>43A-2-2026-1059-113</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 1507657</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -220,6 +247,9 @@
     <x:t>43A-2-2026-1104-763</x:t>
   </x:si>
   <x:si>
+    <x:t>1507790</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -235,6 +265,9 @@
     <x:t>43A-2-2026-1074-021</x:t>
   </x:si>
   <x:si>
+    <x:t>1507743</x:t>
+  </x:si>
+  <x:si>
     <x:t>GIZMOTECH CORPORATION - GAMES AND GADGETS</x:t>
   </x:si>
   <x:si>
@@ -247,6 +280,9 @@
     <x:t>43A-2-2026-1075-295</x:t>
   </x:si>
   <x:si>
+    <x:t>1507742</x:t>
+  </x:si>
+  <x:si>
     <x:t>MUNERIS INCORPORATED (SST LAPTOP)</x:t>
   </x:si>
   <x:si>
@@ -259,6 +295,9 @@
     <x:t>43A-2-2026-1123-290</x:t>
   </x:si>
   <x:si>
+    <x:t>1507839</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station Permit to PURCHASE/POSSESS (DOMESTIC Trade)</x:t>
   </x:si>
   <x:si>
@@ -274,6 +313,9 @@
     <x:t>43A-2-2026-1140-568</x:t>
   </x:si>
   <x:si>
+    <x:t>1507884</x:t>
+  </x:si>
+  <x:si>
     <x:t>RODOLFO C. ABAD JR.</x:t>
   </x:si>
   <x:si>
@@ -286,6 +328,9 @@
     <x:t>43A-2-2026-1141-720</x:t>
   </x:si>
   <x:si>
+    <x:t>1507883</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -313,12 +358,18 @@
     <x:t>43A-3-2026-1210-786</x:t>
   </x:si>
   <x:si>
+    <x:t>1529812</x:t>
+  </x:si>
+  <x:si>
     <x:t>DD-AT-02054C-2026</x:t>
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1209-851</x:t>
   </x:si>
   <x:si>
+    <x:t>1529809</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUBEN C. SESCON</x:t>
   </x:si>
   <x:si>
@@ -331,6 +382,9 @@
     <x:t>43A-3-2026-1203-366</x:t>
   </x:si>
   <x:si>
+    <x:t>1529776</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -343,6 +397,9 @@
     <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
+    <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -353,6 +410,9 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1147-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507892</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -364,7 +424,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -433,13 +493,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -691,7 +744,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -732,50 +785,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -823,6 +867,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -834,71 +882,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1279,7 +1311,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1289,23 +1321,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="16">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="I8" s="16">
+        <x:v>46066.3145039236</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46066.3194212963</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46066.3194256134</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1313,639 +1345,639 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46072.1720853819</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46072.2351628009</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46073.1890290625</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46063.2819612616</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46063.2922791319</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="L10" s="18">
+        <x:v>46063.2957673958</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="C11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46058.4859935069</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46062.1570258102</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46062.1882026968</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="D12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46072.3184291551</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46072.3184479745</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
+      <x:c r="L12" s="18">
+        <x:v>46079.269710081</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46072.3605633333</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46073.2285051968</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46072.352960787</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46073.2314433796</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46073.3142477315</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
+      <x:c r="E16" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46058.1529325347</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46058.1529476968</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46058.2410705671</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s"/>
-      <x:c r="E15" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="E17" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46072.2635348032</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L17" s="18">
+        <x:v>46073.3091133681</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="B18" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46066.2180240509</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="J18" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L18" s="18">
+        <x:v>46066.2724449537</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="B19" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46066.2275385417</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="J19" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L19" s="18">
+        <x:v>46066.2701807986</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="C20" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46078.2436305208</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="J20" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L20" s="18">
+        <x:v>46078.3266231366</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s"/>
-      <x:c r="E21" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="B21" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s"/>
+      <x:c r="E21" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46080.2342400116</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46080.2342615972</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L21" s="18">
+        <x:v>46080.3353454745</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s"/>
-      <x:c r="E22" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
+      <x:c r="B22" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s"/>
+      <x:c r="E22" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46080.272270544</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46080.2722898495</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L22" s="18">
+        <x:v>46080.3345804745</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s"/>
-      <x:c r="D25" s="23" t="s"/>
-      <x:c r="E25" s="24" t="s"/>
-      <x:c r="F25" s="24" t="s"/>
+      <x:c r="B25" s="19" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="21" t="s"/>
+      <x:c r="F25" s="21" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="s">
-        <x:v>89</x:v>
+      <x:c r="B26" s="22" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="s">
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="28" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="28" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="30" t="n">
+      <x:c r="B28" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="B29" s="25" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="28" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
+      <x:c r="B30" s="25" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
+      <x:c r="B31" s="25" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
+      <x:c r="B32" s="25" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
+      <x:c r="B33" s="25" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
+      <x:c r="B34" s="25" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="31" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C35" s="32" t="s"/>
-      <x:c r="D35" s="32" t="s"/>
-      <x:c r="E35" s="32" t="s"/>
-      <x:c r="F35" s="33" t="n">
+      <x:c r="B35" s="28" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -3035,7 +3067,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3114,35 +3146,35 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46100.3734490741</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46100.388599537</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1529812</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46100.3734511921</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46100.3886071759</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46100.3957175926</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46100.3957177662</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -3150,212 +3182,212 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46100.365787037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46100.3731712963</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1529809</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46100.3868981482</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46100.3869012616</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="C10" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46098.0997679745</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="B11" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46085.1627479398</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46085.1627651505</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46090.3453534259</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="B12" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46083.1543707755</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="24" t="s"/>
+      <x:c r="B15" s="19" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="s">
-        <x:v>89</x:v>
+      <x:c r="B16" s="22" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="31" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C20" s="32" t="s"/>
-      <x:c r="D20" s="32" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="33" t="n">
+      <x:c r="B20" s="28" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -385,6 +385,24 @@
     <x:t>1529776</x:t>
   </x:si>
   <x:si>
+    <x:t>GIZHUB GADGETS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95 CZK-16 2nd Floor SM San Mateo General Luna Street, Ampid 1, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-0004C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1219-996</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511284</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -398,6 +416,45 @@
   </x:si>
   <x:si>
     <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUXU CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTC2-K119 Montaban Town Center E. Rodriguez, San Jose, Rodriguez (Montalban), Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-454R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1218-177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTC-K-127 Tanay  Town Center F.T Catapusan, Plaza  Aldea, Tanay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1217-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTC2-K106 B47 Xentro Mall E. Rodriguez Highway Cor.Reyes, Manggahan, Rodriguez (Montalban), Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-455R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1216-073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511285</x:t>
   </x:si>
   <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
@@ -3269,10 +3326,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46085.1627479398</x:v>
+        <x:v>46104.1922695255</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46085.1627651505</x:v>
+        <x:v>46104.1922873958</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>124</x:v>
@@ -3281,121 +3338,279 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46104.342277338</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46083.0936215278</x:v>
+        <x:v>46085.1627479398</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46084</x:v>
+        <x:v>46085.1627651505</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46083.1543707755</x:v>
+        <x:v>46090.3453534259</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46104.1835884259</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46104.3519977083</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46104.177447419</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46104.3503927546</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46104.1653972107</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46104.3486613194</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46083.1543707755</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="19" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="C19" s="20" t="s"/>
+      <x:c r="D19" s="20" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="21" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="22" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="s">
         <x:v>104</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="25" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="25" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="25" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4365,17 +4580,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -346,13 +346,25 @@
     <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
+    <x:t>ARMANDO A. ABECILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>blk.21 lot1 japan st. san marino subd., salawag, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03055C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1222-017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529828</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER I. PALLESCO</x:t>
   </x:si>
   <x:si>
     <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-03055C-2026</x:t>
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1210-786</x:t>
@@ -3216,10 +3228,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46100.3734511921</x:v>
+        <x:v>46105.0657206366</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46100.3886071759</x:v>
+        <x:v>46105.1083022685</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>111</x:v>
@@ -3228,7 +3240,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46100.3957177662</x:v>
+        <x:v>46105.1161564931</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -3239,32 +3251,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46100.3657890856</x:v>
+        <x:v>46100.3734511921</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46100.3731746412</x:v>
+        <x:v>46100.3886071759</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46100.3869012616</x:v>
+        <x:v>46100.3957177662</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -3275,32 +3287,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46098.0792632986</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46098.0878978819</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46098.0997679745</x:v>
+        <x:v>46100.3869012616</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -3308,40 +3320,38 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46104.1922695255</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46104.1922873958</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46104.342277338</x:v>
+        <x:v>46098.0997679745</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -3349,75 +3359,75 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46104.1922695255</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46104.1922873958</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46085.1627479398</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46085.1627651505</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46104.342277338</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46085.1627479398</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46085.1627651505</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46104.1835884259</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46104.3519977083</x:v>
+        <x:v>46090.3453534259</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
@@ -3425,7 +3435,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>47</x:v>
@@ -3440,7 +3450,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46104.177447419</x:v>
+        <x:v>46104.1835884259</x:v>
       </x:c>
       <x:c r="I14" s="16">
         <x:v>46105</x:v>
@@ -3452,10 +3462,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46104.3503927546</x:v>
+        <x:v>46104.3519977083</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -3463,7 +3473,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>47</x:v>
@@ -3478,7 +3488,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46104.1653972107</x:v>
+        <x:v>46104.177447419</x:v>
       </x:c>
       <x:c r="I15" s="16">
         <x:v>46105</x:v>
@@ -3490,128 +3500,165 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46104.3486613194</x:v>
+        <x:v>46104.3503927546</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>144</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46104.1653972107</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46104.3486613194</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46083.0936215278</x:v>
       </x:c>
-      <x:c r="I16" s="16">
+      <x:c r="I17" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L17" s="18">
         <x:v>46083.1543707755</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="19" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="19" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C19" s="20" t="s"/>
-      <x:c r="D19" s="20" t="s"/>
-      <x:c r="E19" s="21" t="s"/>
-      <x:c r="F19" s="21" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="22" t="s">
+      <x:c r="C20" s="20" t="s"/>
+      <x:c r="D20" s="20" t="s"/>
+      <x:c r="E20" s="21" t="s"/>
+      <x:c r="F20" s="21" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="22" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="s">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="s">
         <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="25" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s"/>
       <x:c r="D22" s="26" t="s"/>
       <x:c r="E22" s="26" t="s"/>
       <x:c r="F22" s="27" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
       <x:c r="E23" s="26" t="s"/>
       <x:c r="F23" s="27" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
       <x:c r="E24" s="26" t="s"/>
       <x:c r="F24" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="25" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="28" t="s">
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4585,13 +4632,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
-  <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+  <x:si>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>DONNA GONZALES</x:t>
@@ -380,6 +380,21 @@
   </x:si>
   <x:si>
     <x:t>1529809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GINA O. ILANO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLOCK 8 LOT 21 AGUINALDO ST., ANABU 2-E, Imus City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03056C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1242-732</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529889</x:t>
   </x:si>
   <x:si>
     <x:t>RUBEN C. SESCON</x:t>
@@ -1332,7 +1347,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1372,7 +1387,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1409,7 +1424,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1445,7 +1460,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1481,7 +1496,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1517,7 +1532,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
@@ -1555,7 +1570,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
@@ -1593,7 +1608,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
@@ -1631,7 +1646,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
@@ -1667,7 +1682,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
@@ -1705,7 +1720,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
@@ -1743,7 +1758,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
@@ -1781,7 +1796,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
@@ -1819,7 +1834,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
@@ -1857,7 +1872,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
@@ -1893,7 +1908,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
@@ -3169,7 +3184,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3209,7 +3224,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -3246,7 +3261,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3282,7 +3297,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3318,7 +3333,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3336,10 +3351,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46098.0792632986</x:v>
+        <x:v>46111.2841091551</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46098.0878978819</x:v>
+        <x:v>46111.2878643287</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>123</x:v>
@@ -3348,22 +3363,20 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46098.0997679745</x:v>
+        <x:v>46111.3229630093</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
+      <x:c r="D12" s="15" t="s"/>
       <x:c r="E12" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
@@ -3374,71 +3387,71 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46104.1922695255</x:v>
+        <x:v>46098.0792632986</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46104.1922873958</x:v>
+        <x:v>46098.0878978819</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46104.342277338</x:v>
+        <x:v>46098.0997679745</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46104.1922695255</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46104.1922873958</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46085.1627479398</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46085.1627651505</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46104.342277338</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
         <x:v>136</x:v>
@@ -3450,106 +3463,106 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46104.1835884259</x:v>
+        <x:v>46085.1627479398</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46105</x:v>
+        <x:v>46085.1627651505</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46104.3519977083</x:v>
+        <x:v>46090.3453534259</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46104.177447419</x:v>
+        <x:v>46104.1835884259</x:v>
       </x:c>
       <x:c r="I15" s="16">
         <x:v>46105</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46104.3503927546</x:v>
+        <x:v>46104.3519977083</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46104.1653972107</x:v>
+        <x:v>46104.177447419</x:v>
       </x:c>
       <x:c r="I16" s="16">
         <x:v>46105</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46104.3486613194</x:v>
+        <x:v>46104.3503927546</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>148</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>47</x:v>
@@ -3564,102 +3577,139 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46083.0936215278</x:v>
+        <x:v>46104.1653972107</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46084</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>152</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46104.3486613194</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L17" s="18">
+      <x:c r="L18" s="18">
         <x:v>46083.1543707755</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="19" t="s">
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="19" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C20" s="20" t="s"/>
-      <x:c r="D20" s="20" t="s"/>
-      <x:c r="E20" s="21" t="s"/>
-      <x:c r="F20" s="21" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="22" t="s">
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="22" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="s">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
         <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
       <x:c r="E23" s="26" t="s"/>
       <x:c r="F23" s="27" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
       <x:c r="E24" s="26" t="s"/>
       <x:c r="F24" s="27" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
       <x:c r="E25" s="26" t="s"/>
       <x:c r="F25" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="25" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="28" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4632,13 +4682,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -8,6 +8,7 @@
   <x:sheets>
     <x:sheet name="February 2026" sheetId="7" r:id="rId7"/>
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
+    <x:sheet name="April 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -31,9 +32,6 @@
     <x:t>DONNA GONZALES</x:t>
   </x:si>
   <x:si>
-    <x:t>IV-A | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -343,9 +341,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IV-A | March 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>ARMANDO A. ABECILLA</x:t>
   </x:si>
   <x:si>
@@ -497,6 +492,21 @@
   </x:si>
   <x:si>
     <x:t>1507892</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMAS MIGUEL A. SAPLARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Section D 12 13 Tropical Village, San Francisco, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04057C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1255-170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529908</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -508,7 +518,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -594,6 +604,13 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -828,7 +845,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -845,6 +862,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -902,8 +922,20 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -942,6 +974,10 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -1016,6 +1052,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1313,20 +1361,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1349,719 +1397,719 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46066.3145039236</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46066.3145039236</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46066.3194256134</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46072.1720853819</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46072.2351628009</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46066.3194256134</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46072.1720853819</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46072.2351628009</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="L9" s="19">
+        <x:v>46073.1890290625</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46063.2819612616</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46063.2922791319</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46073.1890290625</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46063.2819612616</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46063.2922791319</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="L10" s="19">
+        <x:v>46063.2957673958</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46058.4859935069</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46062.1570258102</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46063.2957673958</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46058.4859935069</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46062.1570258102</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
+      <x:c r="L11" s="19">
+        <x:v>46062.1882026968</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46062.1882026968</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="C12" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="D12" s="16" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
+      <x:c r="E12" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>46072.3184291551</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46072.3184479745</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46072.3184291551</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46072.3184479745</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46079.269710081</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46072.3605633333</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46073.2285051968</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46072.352960787</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46073.2314433796</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46073.3142477315</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46058.1529325347</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46058.1529476968</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46079.269710081</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="L16" s="19">
+        <x:v>46058.2410705671</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46072.3605633333</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46073.2285051968</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46072.352960787</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46073.2314433796</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46073.2761712037</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46073.2761712037</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46073.3142477315</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46058.1529325347</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46058.1529476968</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46058.2410705671</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="E17" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="F17" s="15" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="G17" s="15" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="H17" s="17">
+        <x:v>46072.2635348032</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46072.2635348032</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
+      <x:c r="K17" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46073.3091133681</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46073.3091133681</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
+      <x:c r="C18" s="15" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="D18" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="F18" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="G18" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="H18" s="17">
+        <x:v>46066.2180240509</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46066.2180240509</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
+      <x:c r="K18" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46066.2724449537</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="D19" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46066.2275385417</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46066.2724449537</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46066.2275385417</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
+      <x:c r="L19" s="19">
+        <x:v>46066.2701807986</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="D20" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46078.2436305208</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46066.2701807986</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46078.2436305208</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
+      <x:c r="L20" s="19">
+        <x:v>46078.3266231366</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46078.3266231366</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
+      <x:c r="C21" s="15" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="D21" s="16" t="s"/>
+      <x:c r="E21" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s"/>
-      <x:c r="E21" s="14" t="s">
+      <x:c r="F21" s="15" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="G21" s="15" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="H21" s="17">
+        <x:v>46080.2342400116</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46080.2342615972</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46080.2342400116</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46080.2342615972</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
+      <x:c r="K21" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46080.3353454745</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="D22" s="16" t="s"/>
+      <x:c r="E22" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46080.272270544</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46080.2722898495</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46080.3353454745</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s"/>
-      <x:c r="E22" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46080.272270544</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46080.2722898495</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
+      <x:c r="L22" s="19">
         <x:v>46080.3345804745</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M22" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="19" t="s">
+      <x:c r="B25" s="20" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C25" s="21" t="s"/>
+      <x:c r="D25" s="21" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="22" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="23" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C25" s="20" t="s"/>
-      <x:c r="D25" s="20" t="s"/>
-      <x:c r="E25" s="21" t="s"/>
-      <x:c r="F25" s="21" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="22" t="s">
+      <x:c r="C26" s="24" t="s"/>
+      <x:c r="D26" s="24" t="s"/>
+      <x:c r="E26" s="24" t="s"/>
+      <x:c r="F26" s="25" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C26" s="23" t="s"/>
-      <x:c r="D26" s="23" t="s"/>
-      <x:c r="E26" s="23" t="s"/>
-      <x:c r="F26" s="24" t="s">
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="26" t="s"/>
-      <x:c r="D27" s="26" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="25" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="25" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="25" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C35" s="29" t="s"/>
-      <x:c r="D35" s="29" t="s"/>
-      <x:c r="E35" s="29" t="s"/>
-      <x:c r="F35" s="30" t="n">
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -3150,20 +3198,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3186,527 +3234,527 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46105.0657206366</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46105.1083022685</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46105.1161564931</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46105.0657206366</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46105.1083022685</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="F9" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46100.3734511921</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46100.3886071759</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46105.1161564931</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="L9" s="19">
+        <x:v>46100.3957177662</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46100.3734511921</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46100.3886071759</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="H10" s="17">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46100.3957177662</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="L10" s="19">
+        <x:v>46100.3869012616</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46100.3657890856</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46100.3731746412</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="F11" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46111.2841091551</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46111.2878643287</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46100.3869012616</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="L11" s="19">
+        <x:v>46111.3229630093</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46111.2841091551</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46111.2878643287</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="F12" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46111.3229630093</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="L12" s="19">
+        <x:v>46098.0997679745</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46098.0792632986</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46098.0878978819</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="D13" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="F13" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46098.0997679745</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="H13" s="17">
+        <x:v>46104.1922695255</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46104.1922873958</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="K13" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46104.342277338</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46104.1922695255</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46104.1922873958</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="D14" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46085.1627479398</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46085.1627651505</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46104.342277338</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="L14" s="19">
+        <x:v>46090.3453534259</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46085.1627479398</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46085.1627651505</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
+      <x:c r="D15" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46090.3453534259</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="F15" s="15" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="G15" s="15" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="H15" s="17">
+        <x:v>46104.1835884259</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="K15" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46104.3519977083</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46104.1835884259</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="F16" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46104.177447419</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="J16" s="16" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46104.3519977083</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="L16" s="19">
+        <x:v>46104.3503927546</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46104.177447419</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
+      <x:c r="F17" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46104.1653972107</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="J17" s="16" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46104.3503927546</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="L17" s="19">
+        <x:v>46104.3486613194</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46104.1653972107</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
+      <x:c r="D18" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46104.3486613194</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="F18" s="15" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="G18" s="15" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="H18" s="17">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46083.0936215278</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="19">
         <x:v>46083.1543707755</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M18" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="19" t="s">
+      <x:c r="B21" s="20" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C21" s="21" t="s"/>
+      <x:c r="D21" s="21" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="22" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="23" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="s"/>
-      <x:c r="D21" s="20" t="s"/>
-      <x:c r="E21" s="21" t="s"/>
-      <x:c r="F21" s="21" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="22" t="s">
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="24" t="s"/>
+      <x:c r="F22" s="25" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="s">
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -4703,4 +4751,1271 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="32" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s"/>
+      <x:c r="E8" s="32" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G8" s="32" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H8" s="33">
+        <x:v>46118.0819693518</x:v>
+      </x:c>
+      <x:c r="I8" s="33">
+        <x:v>46118.1068635995</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K8" s="34" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="33">
+        <x:v>46118.1414470833</x:v>
+      </x:c>
+      <x:c r="M8" s="32" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="20" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="23" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="29" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -492,6 +492,21 @@
   </x:si>
   <x:si>
     <x:t>1507892</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERLYN V. AGUILAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phase 4 block 4 lot 19 Waterfield Village, Tabon 1, Kawit, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04058C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1259-915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529949</x:t>
   </x:si>
   <x:si>
     <x:t>THOMAS MIGUEL A. SAPLARAN</x:t>
@@ -518,7 +533,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -604,13 +619,6 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -845,7 +853,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -922,20 +930,8 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1052,18 +1048,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -4923,99 +4907,121 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="32" t="s">
+      <x:c r="B8" s="15" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="s">
+      <x:c r="C8" s="15" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="s"/>
-      <x:c r="E8" s="32" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G8" s="32" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H8" s="33">
+      <x:c r="H8" s="17">
+        <x:v>46120.234578125</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46120.2626540162</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46120.264807581</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
         <x:v>46118.0819693518</x:v>
       </x:c>
-      <x:c r="I8" s="33">
+      <x:c r="I9" s="17">
         <x:v>46118.1068635995</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="K8" s="34" t="n">
+      <x:c r="J9" s="16" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L9" s="19">
         <x:v>46118.1414470833</x:v>
       </x:c>
-      <x:c r="M8" s="32" t="s">
+      <x:c r="M9" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>103</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6000,10 +6006,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -533,7 +533,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -573,14 +573,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -853,7 +845,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -864,16 +856,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -885,53 +874,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -966,87 +955,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1348,17 +1333,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1381,719 +1366,719 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46066.3145039236</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46066.3194256134</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46072.1720853819</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46072.2351628009</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46073.1890290625</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46063.2819612616</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46063.2922791319</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46063.2957673958</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46058.4859935069</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46062.1570258102</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46062.1882026968</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46072.3184291551</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46072.3184479745</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46079.269710081</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46072.3605633333</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46073.2285051968</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46072.352960787</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46073.2314433796</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46073.2761712037</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46073.2761712037</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46073.3142477315</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46058.1529325347</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46058.1529476968</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46058.2410705671</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46072.2635348032</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46073.3091133681</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46066.2180240509</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46066.2724449537</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46066.2275385417</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46066.2701807986</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46078.2436305208</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46078.3266231366</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s"/>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="D21" s="15" t="s"/>
+      <x:c r="E21" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46080.2342400116</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>46080.2342615972</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46080.3353454745</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s"/>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="D22" s="15" t="s"/>
+      <x:c r="E22" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46080.272270544</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46080.2722898495</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46080.3345804745</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="20" t="s">
+      <x:c r="B25" s="19" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C25" s="21" t="s"/>
-      <x:c r="D25" s="21" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="22" t="s"/>
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="21" t="s"/>
+      <x:c r="F25" s="21" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="23" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="s">
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="s">
         <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
+      <x:c r="B34" s="25" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="29" t="s">
+      <x:c r="B35" s="28" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C35" s="30" t="s"/>
-      <x:c r="D35" s="30" t="s"/>
-      <x:c r="E35" s="30" t="s"/>
-      <x:c r="F35" s="31" t="n">
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -3185,17 +3170,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3218,527 +3203,527 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46105.0657206366</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46105.1083022685</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46105.1161564931</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46100.3734511921</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46100.3886071759</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46100.3957177662</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46100.3657890856</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46100.3731746412</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46100.3869012616</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46111.2841091551</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46111.2878643287</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46111.3229630093</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46098.0792632986</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46098.0878978819</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46098.0997679745</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46104.1922695255</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46104.1922873958</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46104.342277338</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46085.1627479398</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46085.1627651505</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46090.3453534259</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46104.1835884259</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46104.3519977083</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46104.177447419</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46104.3503927546</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46104.1653972107</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46104.3486613194</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46083.0936215278</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46083.1543707755</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="20" t="s">
+      <x:c r="B21" s="19" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C21" s="21" t="s"/>
-      <x:c r="D21" s="21" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="22" t="s"/>
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="23" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="24" t="s"/>
-      <x:c r="F22" s="25" t="s">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
         <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
+      <x:c r="B27" s="28" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -4834,17 +4819,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4867,158 +4852,158 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46120.234578125</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46120.2626540162</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46120.264807581</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46118.0819693518</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46118.1068635995</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46118.1414470833</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -507,6 +507,21 @@
   </x:si>
   <x:si>
     <x:t>1529949</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROEVEN B. DILAO JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>051 Gladiola St. / Sta. Cecilia 1 Subdivision, Mulawin, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04059C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1288-306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530108</x:t>
   </x:si>
   <x:si>
     <x:t>THOMAS MIGUEL A. SAPLARAN</x:t>
@@ -4945,10 +4960,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46118.0819693518</x:v>
+        <x:v>46135.1787023843</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46118.1068635995</x:v>
+        <x:v>46135.2015621759</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>165</x:v>
@@ -4957,57 +4972,92 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46118.1414470833</x:v>
+        <x:v>46135.2084223264</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46118.0819693518</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46118.1068635995</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46118.1414470833</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="19" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>103</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="28" t="s">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="28" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5991,10 +6041,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -507,6 +507,21 @@
   </x:si>
   <x:si>
     <x:t>1529949</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRIAN O. RESPENDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blk 24 lot 59 Malinis st., Pamayanang Maliksi purok 2, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04060C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1296-272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530146</x:t>
   </x:si>
   <x:si>
     <x:t>ROEVEN B. DILAO JR.</x:t>
@@ -4960,10 +4975,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46135.1787023843</x:v>
+        <x:v>46139.2872333449</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46135.2015621759</x:v>
+        <x:v>46139.2954471528</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>165</x:v>
@@ -4972,7 +4987,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46135.2084223264</x:v>
+        <x:v>46139.3359159606</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
@@ -4996,10 +5011,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46118.0819693518</x:v>
+        <x:v>46135.1787023843</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46118.1068635995</x:v>
+        <x:v>46135.2015621759</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>170</x:v>
@@ -5008,57 +5023,92 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46118.1414470833</x:v>
+        <x:v>46135.2084223264</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46118.0819693518</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46118.1068635995</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46118.1414470833</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="19" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>103</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="28" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6041,10 +6091,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DONNA-GONZALES-evaluator-cache-serviceTracking-DONNA-GONZALES-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -68,9 +68,96 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Retailer/Reseller Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAY YOUNG ONLINE TRADING OPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3 M. Salud Road, Alapan II-A, Imus City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-02-0001C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1059-113</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 1507657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
+    <x:t>ROFIEN F. NUÑEZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>415 Gaviño St., Mabolo 2, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02049C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1061-611</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507672</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RASEL C. FERRER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sitio Bantilan, Sapang 1, Ternate, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02050C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1072-268</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Service Center Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIZMOTECH CORPORATION - GAMES AND GADGETS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 28 2/F Cyberzone SM City Rosario Gen. Trias Drive, Tejeros Convention, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-03-0001C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1075-295</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507742</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSZGADGETS CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-25-03-0005C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1074-021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507743</x:t>
+  </x:si>
+  <x:si>
     <x:t>ESTER R. CUENCA</x:t>
   </x:si>
   <x:si>
@@ -86,9 +173,6 @@
     <x:t>1507747</x:t>
   </x:si>
   <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
     <x:t>JORETO S. GABAT</x:t>
   </x:si>
   <x:si>
@@ -104,34 +188,82 @@
     <x:t>1507783</x:t>
   </x:si>
   <x:si>
-    <x:t>RASEL C. FERRER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sitio Bantilan, Sapang 1, Ternate, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-02050C-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1072-268</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROFIEN F. NUÑEZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>415 Gaviño St., Mabolo 2, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-02049C-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1061-611</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507672</x:t>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAR APPLIANCE CENTER, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM City Molino Molino-Paiparan Road, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-13-02-C0327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1107-513</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507784</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAR APPLIANCE CENTER, INC. - (BRANCH)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-13-02-C0328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1106-738</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507785</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMC MOBILE HUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2F E205 SM CITY, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-01-0003C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1104-763</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duplicate Copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGA PIXEL MARKETING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-07-0003C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1114-391</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507791</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MUNERIS INCORPORATED (SST LAPTOP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR E225 CYBERZONE SM CITY DASMARINAS, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-20-03-1030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1123-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507839</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -140,10 +272,7 @@
     <x:t>POLARIS LINKING INC</x:t>
   </x:si>
   <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOWER GROUND LEVEL SPACE 41 AYALA MALL SERIN, SILANG JUNCTION NORTH, Tagaytay City, Cavite</x:t>
+    <x:t>UG MASSWAY SHOPPING CENTER F.T Catapusan, Plaza Almeda, Tanay, Rizal</x:t>
   </x:si>
   <x:si>
     <x:t>DD-MP-26-02-0001C</x:t>
@@ -158,153 +287,27 @@
     <x:t>Deniel Puyo</x:t>
   </x:si>
   <x:si>
-    <x:t>Dealer Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STAR APPLIANCE CENTER, INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM City Molino Molino-Paiparan Road, Molino IV, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-13-02-C0327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1107-513</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507784</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STAR APPLIANCE CENTER, INC. - (BRANCH)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CITY ROSARIO GEN. TRIAS DRIVE, TEJEROS CONVENTION, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-13-02-C0328</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1106-738</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507785</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Duplicate Copy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGA PIXEL MARKETING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2F E205 SM CITY, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-24-07-0003C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1114-391</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507791</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STAY YOUNG ONLINE TRADING OPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3 M. Salud Road, Alapan II-A, Imus City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-02-0001C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1059-113</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 1507657</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMC MOBILE HUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/F Robinsons Place Imus, Tanzang luma V, Imus City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-01-0003C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1104-763</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Service Center Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSZGADGETS CELLPHONE AND ACCESSORIES SHOP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZ 11 Cyberzone SM City Rosario Gen. Trias Drive, Tejeros Convention, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-25-03-0005C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1074-021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507743</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIZMOTECH CORPORATION - GAMES AND GADGETS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 28 2/F Cyberzone SM City Rosario Gen. Trias Drive, Tejeros Convention, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-24-03-0001C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1075-295</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507742</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MUNERIS INCORPORATED (SST LAPTOP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR E225 CYBERZONE SM CITY DASMARINAS, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-20-03-1030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1123-290</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507839</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ship Station Permit to PURCHASE/POSSESS (DOMESTIC Trade)</x:t>
   </x:si>
   <x:si>
+    <x:t>RODOLFO C. ABAD JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amaya V, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MS-02002C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1141-720</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507883</x:t>
+  </x:si>
+  <x:si>
     <x:t>JENNIFER B. ESGUERRA</x:t>
   </x:si>
   <x:si>
-    <x:t>Amaya VII, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-MS-02001C-2026</x:t>
   </x:si>
   <x:si>
@@ -314,21 +317,6 @@
     <x:t>1507884</x:t>
   </x:si>
   <x:si>
-    <x:t>RODOLFO C. ABAD JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amaya V, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MS-02002C-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1141-720</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507883</x:t>
-  </x:si>
-  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -341,42 +329,135 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLOOR SM DASMARIÑAS GOVERNORS DRIVE, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-25-03-0006C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1147-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507892</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBEN C. SESCON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blk. 17, Lot 14, Phase 2 Aquino Street, Citihomes, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIV-A-07321-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1203-366</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHRISTOPHER I. PALLESCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02054C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1209-851</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03055C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1210-786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIZHUB GADGETS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95 CZK-16 2nd Floor SM San Mateo General Luna Street, Ampid 1, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-0004C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1219-996</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511284</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUXU CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-455R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1216-073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511285</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1217-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-454R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1218-177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511287</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMANDO A. ABECILLA</x:t>
   </x:si>
   <x:si>
     <x:t>blk.21 lot1 japan st. san marino subd., salawag, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
-    <x:t>DD-AT-03055C-2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>43A-3-2026-1222-017</x:t>
   </x:si>
   <x:si>
     <x:t>1529828</x:t>
   </x:si>
   <x:si>
-    <x:t>CHRISTOPHER I. PALLESCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1210-786</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1529812</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-02054C-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1209-851</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1529809</x:t>
-  </x:si>
-  <x:si>
     <x:t>GINA O. ILANO</x:t>
   </x:si>
   <x:si>
@@ -392,106 +473,19 @@
     <x:t>1529889</x:t>
   </x:si>
   <x:si>
-    <x:t>RUBEN C. SESCON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Blk. 17, Lot 14, Phase 2 Aquino Street, Citihomes, Molino IV, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIV-A-07321-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1203-366</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1529776</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIZHUB GADGETS AND ACCESSORIES SHOP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95 CZK-16 2nd Floor SM San Mateo General Luna Street, Ampid 1, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-0004C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1219-996</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511284</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUXU CELLPHONE AND ACCESSORIES SHOP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTC2-K119 Montaban Town Center E. Rodriguez, San Jose, Rodriguez (Montalban), Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-325-454R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1218-177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTC-K-127 Tanay  Town Center F.T Catapusan, Plaza  Aldea, Tanay, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-325-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1217-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511286</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTC2-K106 B47 Xentro Mall E. Rodriguez Highway Cor.Reyes, Manggahan, Rodriguez (Montalban), Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-325-455R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1216-073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511285</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLOOR SM DASMARIÑAS GOVERNORS DRIVE, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-25-03-0006C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1147-453</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507892</x:t>
+    <x:t>THOMAS MIGUEL A. SAPLARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Section D 12 13 Tropical Village, San Francisco, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04057C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1255-170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529908</x:t>
   </x:si>
   <x:si>
     <x:t>BERLYN V. AGUILAR</x:t>
@@ -509,6 +503,21 @@
     <x:t>1529949</x:t>
   </x:si>
   <x:si>
+    <x:t>ROEVEN B. DILAO JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>051 Gladiola St. / Sta. Cecilia 1 Subdivision, Mulawin, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04059C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1288-306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530108</x:t>
+  </x:si>
+  <x:si>
     <x:t>BRIAN O. RESPENDE</x:t>
   </x:si>
   <x:si>
@@ -522,36 +531,6 @@
   </x:si>
   <x:si>
     <x:t>1530146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROEVEN B. DILAO JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>051 Gladiola St. / Sta. Cecilia 1 Subdivision, Mulawin, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-04059C-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1288-306</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMAS MIGUEL A. SAPLARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Section D 12 13 Tropical Village, San Francisco, General Trias, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-04057C-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1255-170</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1529908</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1442,87 +1421,89 @@
       <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
+      <x:c r="D8" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46066.2950925926</x:v>
+        <x:v>46058.1529325347</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46066.3145039236</x:v>
+        <x:v>46058.1529476968</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46066.3194256134</x:v>
+        <x:v>46058.2410705671</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46072.1720853819</x:v>
+        <x:v>46058.4859935069</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46072.2351628009</x:v>
+        <x:v>46062.1570258102</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46073.1890290625</x:v>
+        <x:v>46062.1882026968</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H10" s="16">
         <x:v>46063.2819612616</x:v>
@@ -1531,7 +1512,7 @@
         <x:v>46063.2922791319</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
@@ -1540,251 +1521,251 @@
         <x:v>46063.2957673958</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46058.4859935069</x:v>
+        <x:v>46066.2275385417</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46062.1570258102</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46062.1882026968</x:v>
+        <x:v>46066.2701807986</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46072.3184291551</x:v>
+        <x:v>46066.2180240509</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46072.3184479745</x:v>
+        <x:v>46083</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46079.269710081</x:v>
+        <x:v>46066.2724449537</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46066.3145039236</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46072.3605633333</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46073.2285051968</x:v>
+        <x:v>46066.3194256134</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46072.1720853819</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46072.2351628009</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46072.352960787</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46073.2314433796</x:v>
+        <x:v>46073.1890290625</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46072.3605633333</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46073.2761712037</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46073.2761712037</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>150</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46073.3142477315</x:v>
+        <x:v>46073.2285051968</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46072.352960787</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46058.1529325347</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46058.1529476968</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46058.2410705671</x:v>
+        <x:v>46073.2314433796</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="16">
         <x:v>46072.2635348032</x:v>
@@ -1793,7 +1774,7 @@
         <x:v>46055</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3780</x:v>
@@ -1802,200 +1783,198 @@
         <x:v>46073.3091133681</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46066.2180240509</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46066.2724449537</x:v>
+        <x:v>46073.3142477315</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46066.2275385417</x:v>
+        <x:v>46078.2436305208</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46100</x:v>
+        <x:v>46085</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46066.2701807986</x:v>
+        <x:v>46078.3266231366</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46072.3184291551</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46072.3184479745</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
+      <x:c r="K20" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46079.269710081</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46078.2436305208</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46078.3266231366</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s"/>
       <x:c r="E21" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46080.272270544</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46080.2722898495</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46080.2342400116</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46080.2342615972</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46080.3353454745</x:v>
+        <x:v>46080.3345804745</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s"/>
       <x:c r="E22" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46080.272270544</x:v>
+        <x:v>46080.2342400116</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46080.2722898495</x:v>
+        <x:v>46080.2342615972</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46080.3345804745</x:v>
+        <x:v>46080.3353454745</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="19" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C25" s="20" t="s"/>
       <x:c r="D25" s="20" t="s"/>
@@ -2004,18 +1983,18 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
       <x:c r="B26" s="22" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C26" s="23" t="s"/>
       <x:c r="D26" s="23" t="s"/>
       <x:c r="E26" s="23" t="s"/>
       <x:c r="F26" s="24" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C27" s="26" t="s"/>
       <x:c r="D27" s="26" t="s"/>
@@ -2026,7 +2005,7 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="25" t="s">
-        <x:v>36</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C28" s="26" t="s"/>
       <x:c r="D28" s="26" t="s"/>
@@ -2037,7 +2016,7 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="25" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C29" s="26" t="s"/>
       <x:c r="D29" s="26" t="s"/>
@@ -2048,7 +2027,7 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
@@ -2059,7 +2038,7 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
@@ -2070,7 +2049,7 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
@@ -2081,7 +2060,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="25" t="s">
-        <x:v>74</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="26" t="s"/>
       <x:c r="D33" s="26" t="s"/>
@@ -2092,7 +2071,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="25" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C34" s="26" t="s"/>
       <x:c r="D34" s="26" t="s"/>
@@ -2103,7 +2082,7 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C35" s="29" t="s"/>
       <x:c r="D35" s="29" t="s"/>
@@ -3274,38 +3253,40 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46105.0657206366</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46105.1083022685</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46105.1161564931</x:v>
+        <x:v>46083.1543707755</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
@@ -3313,163 +3294,165 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46085.1627479398</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46085.1627651505</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46100.3734511921</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46100.3886071759</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46100.3957177662</x:v>
+        <x:v>46090.3453534259</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46100.3657890856</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46100.3731746412</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46100.3869012616</x:v>
+        <x:v>46098.0997679745</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46111.2841091551</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46111.2878643287</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46111.3229630093</x:v>
+        <x:v>46100.3869012616</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s"/>
       <x:c r="E12" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46100.3734511921</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46100.3886071759</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46098.0792632986</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46098.0878978819</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46098.0997679745</x:v>
+        <x:v>46100.3957177662</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="H13" s="16">
         <x:v>46104.1922695255</x:v>
@@ -3478,7 +3461,7 @@
         <x:v>46104.1922873958</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3530</x:v>
@@ -3487,204 +3470,200 @@
         <x:v>46104.342277338</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46104.1653972107</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46085.1627479398</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46085.1627651505</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46104.3486613194</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>138</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>139</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46104.1835884259</x:v>
+        <x:v>46104.177447419</x:v>
       </x:c>
       <x:c r="I15" s="16">
         <x:v>46105</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>142</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46104.3519977083</x:v>
+        <x:v>46104.3503927546</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
       <x:c r="H16" s="16">
-        <x:v>46104.177447419</x:v>
+        <x:v>46104.1835884259</x:v>
       </x:c>
       <x:c r="I16" s="16">
         <x:v>46105</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>146</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46104.3503927546</x:v>
+        <x:v>46104.3519977083</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s"/>
       <x:c r="E17" s="14" t="s">
-        <x:v>147</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>148</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>149</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46104.1653972107</x:v>
+        <x:v>46105.0657206366</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46105</x:v>
+        <x:v>46105.1083022685</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>150</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46104.3486613194</x:v>
+        <x:v>46105.1161564931</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
       <x:c r="E18" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>153</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>154</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46083.0936215278</x:v>
+        <x:v>46111.2841091551</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46084</x:v>
+        <x:v>46111.2878643287</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>155</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46083.1543707755</x:v>
+        <x:v>46111.3229630093</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="19" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C21" s="20" t="s"/>
       <x:c r="D21" s="20" t="s"/>
@@ -3693,18 +3672,18 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
       <x:c r="B22" s="22" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C22" s="23" t="s"/>
       <x:c r="D22" s="23" t="s"/>
       <x:c r="E22" s="23" t="s"/>
       <x:c r="F22" s="24" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
@@ -3715,7 +3694,7 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
@@ -3726,7 +3705,7 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
@@ -3737,7 +3716,7 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="25" t="s">
-        <x:v>74</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C26" s="26" t="s"/>
       <x:c r="D26" s="26" t="s"/>
@@ -3748,7 +3727,7 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
       <x:c r="B27" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C27" s="29" t="s"/>
       <x:c r="D27" s="29" t="s"/>
@@ -4923,92 +4902,92 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>156</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>157</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>158</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>159</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46120.234578125</x:v>
+        <x:v>46118.0819693518</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46120.2626540162</x:v>
+        <x:v>46118.1068635995</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>160</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46120.264807581</x:v>
+        <x:v>46118.1414470833</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>161</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>163</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>164</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46139.2872333449</x:v>
+        <x:v>46120.234578125</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46139.2954471528</x:v>
+        <x:v>46120.2626540162</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>165</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46139.3359159606</x:v>
+        <x:v>46120.264807581</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>166</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>168</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>169</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H10" s="16">
         <x:v>46135.1787023843</x:v>
@@ -5017,7 +4996,7 @@
         <x:v>46135.2015621759</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>170</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
@@ -5026,50 +5005,50 @@
         <x:v>46135.2084223264</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>173</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>174</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46118.0819693518</x:v>
+        <x:v>46139.2872333449</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46118.1068635995</x:v>
+        <x:v>46139.2954471528</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>175</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46118.1414470833</x:v>
+        <x:v>46139.3359159606</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="19" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C14" s="20" t="s"/>
       <x:c r="D14" s="20" t="s"/>
@@ -5078,18 +5057,18 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
       <x:c r="B15" s="22" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C15" s="23" t="s"/>
       <x:c r="D15" s="23" t="s"/>
       <x:c r="E15" s="23" t="s"/>
       <x:c r="F15" s="24" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="26" t="s"/>
       <x:c r="D16" s="26" t="s"/>
@@ -5100,7 +5079,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
       <x:c r="B17" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s"/>
       <x:c r="D17" s="29" t="s"/>
